--- a/reports/pdf_change_20261023.xlsx
+++ b/reports/pdf_change_20261023.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,594억   ·   현금 27억(0.6%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 5종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,380억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 5종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>135</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1349978590</v>
+        <v>1349978481</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-34</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2174069106</v>
+        <v>-2174068931</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>47</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1387975995</v>
+        <v>1387975884</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-31</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1296792182</v>
+        <v>-1296792078</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2151360302</v>
+        <v>2151360130</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-25</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1142910161</v>
+        <v>-1142910069</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1307250184</v>
+        <v>1307250079</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-8</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2027856285</v>
+        <v>-2027856122</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2218590312</v>
+        <v>2218590134</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-6</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-122508017</v>
+        <v>-122508007</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>-5</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1020900144</v>
+        <v>-1020900062</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,216억   ·   현금 60억(1.9%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,140억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -935,7 +935,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,348억   ·   현금 37억(1.7%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 6종목  /  매도 10종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,218억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 6종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1031,7 +1031,7 @@
         <v>300</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2004813303</v>
+        <v>2001778908</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>-230</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-7358253113</v>
+        <v>-7347115992</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1068,23 +1068,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>엘리스</t>
+          <t>코세스  (신규)</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>9280441404</v>
+        <v>3776847940</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.14%→5.66%</t>
+          <t>0.00%→1.73%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>50→200</t>
+          <t>0→150</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1096,7 +1096,7 @@
         <v>-202</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1046812638</v>
+        <v>-1045228230</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1112,23 +1112,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>코세스  (신규)</t>
+          <t>엘리스</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3782573072</v>
+        <v>9266394946</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.73%</t>
+          <t>1.14%→5.66%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>0→150</t>
+          <t>50→200</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1140,7 +1140,7 @@
         <v>-97</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1641395448</v>
+        <v>-1638911106</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>80</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3743904566</v>
+        <v>3738237961</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>-65</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1804530273</v>
+        <v>-1801799017</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>50</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>3592535544</v>
+        <v>3587098043</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>-45</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-3236256490</v>
+        <v>-3231358237</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>30</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2074218314</v>
+        <v>2071078870</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>-39</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-2487673876</v>
+        <v>-2483908645</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>-37</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-4566122591</v>
+        <v>-4559211513</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>-19</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-3152309477</v>
+        <v>-3147538283</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>-16</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1094616166</v>
+        <v>-1092959404</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>-7</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1221528185</v>
+        <v>-1219679335</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,142억   ·   현금 1억(0.1%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 2종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,131억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1496,7 +1496,7 @@
         <v>102</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1008718800</v>
+        <v>1034320902</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>-242</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1973703600</v>
+        <v>-2023797800</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>51</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2121926400</v>
+        <v>2175782615</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>-62</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1003990800</v>
+        <v>-1029472902</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 258억   ·   현금 2억(0.9%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 4종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 248억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1673,11 +1673,11 @@
         <v>132</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>76369920</v>
+        <v>68851178</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>7.06%→7.36%</t>
+          <t>6.64%→6.92%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1694,11 +1694,11 @@
         <v>-26</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-83699200</v>
+        <v>-82284774</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>3.25%→2.92%</t>
+          <t>3.33%→2.99%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1717,11 +1717,11 @@
         <v>31</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>67456000</v>
+        <v>67356779</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>7.02%→7.28%</t>
+          <t>7.30%→7.58%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1738,11 +1738,11 @@
         <v>-24</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-87398400</v>
+        <v>-85862373</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>4.54%→4.20%</t>
+          <t>4.65%→4.30%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1761,11 +1761,11 @@
         <v>10</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>42944000</v>
+        <v>39871988</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>1.06%→1.22%</t>
+          <t>1.02%→1.19%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1782,11 +1782,11 @@
         <v>-15</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-61632000</v>
+        <v>-67967979</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>1.45%→1.20%</t>
+          <t>1.66%→1.38%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1805,11 +1805,11 @@
         <v>7</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>53804800</v>
+        <v>48742385</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>2.31%→2.52%</t>
+          <t>2.18%→2.38%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1867,7 +1867,7 @@
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 863억   ·   현금 2억(0.3%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 3종목  /  매도 9종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 3종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B49" s="4" t="n"/>
@@ -1963,7 +1963,7 @@
         <v>167</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>766029000</v>
+        <v>775313921</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>-334</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-788073000</v>
+        <v>-797625113</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>88</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>685344000</v>
+        <v>693650951</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>-56</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-242550000</v>
+        <v>-245489912</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>46</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>793914000</v>
+        <v>803536911</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>-36</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-155925000</v>
+        <v>-157814943</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>-24</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-243540000</v>
+        <v>-246491911</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>-7</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-285862500</v>
+        <v>-289327396</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-13365000</v>
+        <v>-13526995</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>-6</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-214830000</v>
+        <v>-217433922</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>-5</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-139012500</v>
+        <v>-140697449</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>-4</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-167970000</v>
+        <v>-170005939</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2352,11 +2352,11 @@
         <v>20</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>359534084</v>
+        <v>351848082</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>0.53%→1.70%</t>
+          <t>0.53%→1.72%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2373,11 +2373,11 @@
         <v>-68</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-128048790</v>
+        <v>-116579567</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>1.87%→1.46%</t>
+          <t>1.76%→1.37%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2396,11 +2396,11 @@
         <v>9</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>96459323</v>
+        <v>94922122</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.73%→1.05%</t>
+          <t>0.74%→1.06%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2417,11 +2417,11 @@
         <v>-53</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-81697929</v>
+        <v>-75813868</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.00%</t>
+          <t>0.25%→0.00%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2440,11 +2440,11 @@
         <v>7</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>319524175</v>
+        <v>315638474</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>2.68%→3.73%</t>
+          <t>2.73%→3.79%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2461,11 +2461,11 @@
         <v>-41</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-137254912</v>
+        <v>-128326340</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>3.39%→2.95%</t>
+          <t>3.27%→2.84%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2489,11 +2489,11 @@
         <v>-25</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-118919528</v>
+        <v>-107710775</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.00%</t>
+          <t>0.36%→0.00%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2517,11 +2517,11 @@
         <v>-23</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-113432577</v>
+        <v>-108816705</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.64%</t>
+          <t>1.00%→0.64%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2545,11 +2545,11 @@
         <v>-11</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-159698037</v>
+        <v>-159463187</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>4.78%→4.27%</t>
+          <t>4.92%→4.39%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2573,11 +2573,11 @@
         <v>-9</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-42196150</v>
+        <v>-39313899</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.21%</t>
+          <t>0.34%→0.21%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -2601,11 +2601,11 @@
         <v>-6</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-38122569</v>
+        <v>-37456449</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.23%</t>
+          <t>0.36%→0.23%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -2629,11 +2629,11 @@
         <v>-5</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-118279028</v>
+        <v>-116784527</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.39%</t>
+          <t>0.79%→0.39%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -2657,11 +2657,11 @@
         <v>-4</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-117852028</v>
+        <v>-119218428</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>3.46%→3.08%</t>
+          <t>3.61%→3.21%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">

--- a/reports/pdf_change_20261023.xlsx
+++ b/reports/pdf_change_20261023.xlsx
@@ -1068,23 +1068,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>코세스  (신규)</t>
+          <t>엘리스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>3776847940</v>
+        <v>9266394946</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.73%</t>
+          <t>1.14%→5.66%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>0→150</t>
+          <t>50→200</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1112,23 +1112,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>엘리스</t>
+          <t>코세스  (신규)</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9266394946</v>
+        <v>3776847940</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.14%→5.66%</t>
+          <t>0.00%→1.73%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>50→200</t>
+          <t>0→150</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">

--- a/reports/pdf_change_20261023.xlsx
+++ b/reports/pdf_change_20261023.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,13 +62,8 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -100,11 +95,6 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -132,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -172,10 +162,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 9/10  ·  전일분: TIGER 기술이전, TIGER 코스닥, MIDAS  ·  대기: RISE</t>
+          <t>캡처 10/10  ·  전부 반영 완료</t>
         </is>
       </c>
     </row>
@@ -1068,23 +1054,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>엘리스</t>
+          <t>코세스  (신규)</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>9266394946</v>
+        <v>3776847940</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.14%→5.66%</t>
+          <t>0.00%→1.73%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>50→200</t>
+          <t>0→150</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1112,23 +1098,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>코세스  (신규)</t>
+          <t>엘리스</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3776847940</v>
+        <v>9266394946</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.73%</t>
+          <t>1.14%→5.66%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>0→150</t>
+          <t>50→200</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1824,376 +1810,392 @@
       <c r="K42" s="17" t="n"/>
     </row>
     <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="n"/>
-      <c r="C44" s="20" t="n"/>
-      <c r="D44" s="20" t="n"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="20" t="n"/>
-      <c r="G44" s="20" t="n"/>
-      <c r="H44" s="20" t="n"/>
-      <c r="I44" s="20" t="n"/>
-      <c r="J44" s="20" t="n"/>
-      <c r="K44" s="20" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,106억      ※전일분  PDF 2026-10-22  vs  2026-10-21      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 429억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 50억(4.7%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 0종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n"/>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>와이바이오로직스</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-73311907</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.37%→0.20%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>15→11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="n"/>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-432639996</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>7.70%→5.22%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>40→37</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 3종목  /  매도 9종목</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
+      <c r="I55" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K55" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>에스티아이</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n">
+      <c r="B56" s="11" t="n">
         <v>167</v>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C56" s="11" t="n">
         <v>775313921</v>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>2.03%→2.93%</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>365→532</t>
         </is>
       </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>엠케이전자</t>
         </is>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H56" s="15" t="n">
         <v>-334</v>
       </c>
-      <c r="I52" s="15" t="n">
+      <c r="I56" s="15" t="n">
         <v>-797625113</v>
       </c>
-      <c r="J52" s="16" t="inlineStr">
+      <c r="J56" s="16" t="inlineStr">
         <is>
           <t>3.02%→2.00%</t>
         </is>
       </c>
-      <c r="K52" s="13" t="inlineStr">
+      <c r="K56" s="13" t="inlineStr">
         <is>
           <t>1,041→707</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>RFHIC  (신규)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n">
+      <c r="B57" s="11" t="n">
         <v>88</v>
       </c>
-      <c r="C53" s="11" t="n">
+      <c r="C57" s="11" t="n">
         <v>693650951</v>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>0.00%→0.82%</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>0→88</t>
         </is>
       </c>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="G57" s="14" t="inlineStr">
         <is>
           <t>태웅</t>
         </is>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H57" s="15" t="n">
         <v>-56</v>
       </c>
-      <c r="I53" s="15" t="n">
+      <c r="I57" s="15" t="n">
         <v>-245489912</v>
       </c>
-      <c r="J53" s="16" t="inlineStr">
+      <c r="J57" s="16" t="inlineStr">
         <is>
           <t>0.50%→0.20%</t>
         </is>
       </c>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="K57" s="13" t="inlineStr">
         <is>
           <t>95→39</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n">
+      <c r="B58" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="C54" s="11" t="n">
+      <c r="C58" s="11" t="n">
         <v>803536911</v>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>1.01%→1.99%</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>50→96</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>SFA</t>
         </is>
       </c>
-      <c r="H54" s="15" t="n">
+      <c r="H58" s="15" t="n">
         <v>-36</v>
       </c>
-      <c r="I54" s="15" t="n">
+      <c r="I58" s="15" t="n">
         <v>-157814943</v>
       </c>
-      <c r="J54" s="16" t="inlineStr">
+      <c r="J58" s="16" t="inlineStr">
         <is>
           <t>0.69%→0.50%</t>
         </is>
       </c>
-      <c r="K54" s="13" t="inlineStr">
+      <c r="K58" s="13" t="inlineStr">
         <is>
           <t>133→97</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="n"/>
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="17" t="n"/>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="17" t="n"/>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>프로텍</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>-246491911</v>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>0.71%→0.40%</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>57→33</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="17" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>파크시스템스</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <v>-289327396</v>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>1.93%→1.62%</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>40→33</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="n"/>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="17" t="n"/>
-      <c r="D57" s="17" t="n"/>
-      <c r="E57" s="17" t="n"/>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>뉴파워프라즈마</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I57" s="15" t="n">
-        <v>-13526995</v>
-      </c>
-      <c r="J57" s="16" t="inlineStr">
-        <is>
-          <t>3.61%→3.65%</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>1,373→1,367</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="n"/>
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="17" t="n"/>
-      <c r="D58" s="17" t="n"/>
-      <c r="E58" s="17" t="n"/>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>티씨케이</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I58" s="15" t="n">
-        <v>-217433922</v>
-      </c>
-      <c r="J58" s="16" t="inlineStr">
-        <is>
-          <t>0.58%→0.30%</t>
-        </is>
-      </c>
-      <c r="K58" s="13" t="inlineStr">
-        <is>
-          <t>13→7</t>
         </is>
       </c>
     </row>
@@ -2205,23 +2207,23 @@
       <c r="E59" s="17" t="n"/>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>프로텍</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-5</v>
+        <v>-24</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-140697449</v>
+        <v>-246491911</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.43%→2.13%</t>
+          <t>0.71%→0.40%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>69→64</t>
+          <t>57→33</t>
         </is>
       </c>
     </row>
@@ -2233,384 +2235,400 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-289327396</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>1.93%→1.62%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>40→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="n"/>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-217433922</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>0.58%→0.30%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>13→7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n"/>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-13526995</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>3.61%→3.65%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>1,373→1,367</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-140697449</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>2.43%→2.13%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>69→64</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
           <t>티에스이</t>
         </is>
       </c>
-      <c r="H60" s="15" t="n">
+      <c r="H64" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I60" s="15" t="n">
+      <c r="I64" s="15" t="n">
         <v>-170005939</v>
       </c>
-      <c r="J60" s="16" t="inlineStr">
+      <c r="J64" s="16" t="inlineStr">
         <is>
           <t>2.40%→2.11%</t>
         </is>
       </c>
-      <c r="K60" s="13" t="inlineStr">
+      <c r="K64" s="13" t="inlineStr">
         <is>
           <t>46→42</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 311억      ※전일분  PDF 2026-10-22  vs  2026-10-21      매수 3종목  /  매도 10종목</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="4" t="n"/>
-      <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="n"/>
-      <c r="J62" s="4" t="n"/>
-      <c r="K62" s="4" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억   ·   현금 7억(2.2%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 4종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="8" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="G68" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="H68" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
+      <c r="I68" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J64" s="9" t="inlineStr">
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K64" s="9" t="inlineStr">
+      <c r="K68" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>지투지바이오</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="C65" s="11" t="n">
-        <v>351848082</v>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>0.53%→1.72%</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>9→29</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>파인엠텍  (신규)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>333963630</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.13%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>0→77</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>동국산업</t>
         </is>
       </c>
-      <c r="H65" s="15" t="n">
-        <v>-68</v>
-      </c>
-      <c r="I65" s="15" t="n">
-        <v>-116579567</v>
-      </c>
-      <c r="J65" s="16" t="inlineStr">
-        <is>
-          <t>1.76%→1.37%</t>
-        </is>
-      </c>
-      <c r="K65" s="13" t="inlineStr">
-        <is>
-          <t>305→237</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>알지노믹스</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="n">
+      <c r="H69" s="15" t="n">
+        <v>-69</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-118848015</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>1.37%→0.98%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>237→168</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템  (신규)</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>94922122</v>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>0.74%→1.06%</t>
-        </is>
-      </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>21→30</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>피엠티  (편출)</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="n">
-        <v>-53</v>
-      </c>
-      <c r="I66" s="15" t="n">
-        <v>-75813868</v>
-      </c>
-      <c r="J66" s="16" t="inlineStr">
-        <is>
-          <t>0.25%→0.00%</t>
-        </is>
-      </c>
-      <c r="K66" s="13" t="inlineStr">
-        <is>
-          <t>53→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>올릭스</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="n">
+      <c r="C70" s="11" t="n">
+        <v>313513200</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.06%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>0→9</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-63</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-232972740</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>2.97%→2.21%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>240→177</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C67" s="11" t="n">
-        <v>315638474</v>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>2.73%→3.79%</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>18→25</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
-        <is>
-          <t>피노</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n">
-        <v>-41</v>
-      </c>
-      <c r="I67" s="15" t="n">
-        <v>-128326340</v>
-      </c>
-      <c r="J67" s="16" t="inlineStr">
-        <is>
-          <t>3.27%→2.84%</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>311→270</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="17" t="n"/>
-      <c r="B68" s="17" t="n"/>
-      <c r="C68" s="17" t="n"/>
-      <c r="D68" s="17" t="n"/>
-      <c r="E68" s="17" t="n"/>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>HT로보틱스  (편출)</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I68" s="15" t="n">
-        <v>-107710775</v>
-      </c>
-      <c r="J68" s="16" t="inlineStr">
-        <is>
-          <t>0.36%→0.00%</t>
-        </is>
-      </c>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>25→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="17" t="n"/>
-      <c r="B69" s="17" t="n"/>
-      <c r="C69" s="17" t="n"/>
-      <c r="D69" s="17" t="n"/>
-      <c r="E69" s="17" t="n"/>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>덕산하이메탈</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="n">
-        <v>-23</v>
-      </c>
-      <c r="I69" s="15" t="n">
-        <v>-108816705</v>
-      </c>
-      <c r="J69" s="16" t="inlineStr">
-        <is>
-          <t>1.00%→0.64%</t>
-        </is>
-      </c>
-      <c r="K69" s="13" t="inlineStr">
-        <is>
-          <t>63→40</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="17" t="n"/>
-      <c r="B70" s="17" t="n"/>
-      <c r="C70" s="17" t="n"/>
-      <c r="D70" s="17" t="n"/>
-      <c r="E70" s="17" t="n"/>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H70" s="15" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I70" s="15" t="n">
-        <v>-159463187</v>
-      </c>
-      <c r="J70" s="16" t="inlineStr">
-        <is>
-          <t>4.92%→4.39%</t>
-        </is>
-      </c>
-      <c r="K70" s="13" t="inlineStr">
-        <is>
-          <t>101→90</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="17" t="n"/>
-      <c r="B71" s="17" t="n"/>
-      <c r="C71" s="17" t="n"/>
-      <c r="D71" s="17" t="n"/>
-      <c r="E71" s="17" t="n"/>
+      <c r="C71" s="11" t="n">
+        <v>127327200</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>0.55%→0.98%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>9→16</t>
+        </is>
+      </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>덕산테코피아</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-39313899</v>
+        <v>-81750240</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.21%</t>
+          <t>0.91%→0.64%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>23→14</t>
+          <t>40→28</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="17" t="n"/>
-      <c r="B72" s="17" t="n"/>
-      <c r="C72" s="17" t="n"/>
-      <c r="D72" s="17" t="n"/>
-      <c r="E72" s="17" t="n"/>
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>한라IMS</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>18815940</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>0.23%→0.30%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>11→14</t>
+        </is>
+      </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>한라IMS</t>
+          <t>오이솔루션</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-37456449</v>
+        <v>-77177100</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.23%</t>
+          <t>1.03%→0.78%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>17→11</t>
+          <t>28→21</t>
         </is>
       </c>
     </row>
@@ -2622,107 +2640,307 @@
       <c r="E73" s="17" t="n"/>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H73" s="15" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-116784527</v>
+        <v>-201115200</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.39%</t>
+          <t>1.68%→1.02%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
         <is>
-          <t>10→5</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="17" t="n"/>
-      <c r="B74" s="17" t="n"/>
-      <c r="C74" s="17" t="n"/>
-      <c r="D74" s="17" t="n"/>
-      <c r="E74" s="17" t="n"/>
-      <c r="G74" s="14" t="inlineStr">
-        <is>
-          <t>펌텍코리아</t>
-        </is>
-      </c>
-      <c r="H74" s="15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I74" s="15" t="n">
-        <v>-119218428</v>
-      </c>
-      <c r="J74" s="16" t="inlineStr">
-        <is>
-          <t>3.61%→3.21%</t>
-        </is>
-      </c>
-      <c r="K74" s="13" t="inlineStr">
-        <is>
-          <t>36→32</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="19" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억      ※전일분  PDF 2026-10-22  vs  2026-10-21      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="n"/>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="n"/>
-      <c r="J76" s="4" t="n"/>
-      <c r="K76" s="4" t="n"/>
+          <t>10→6</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트  (신규)</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>28441600</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.51%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>0→176</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I78" s="15" t="n">
+        <v>-27283200</v>
+      </c>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>3.44%→2.93%</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>683→585</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>21974400</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>3.18%→3.57%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>449→505</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>-24371200</v>
+      </c>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>4.36%→3.90%</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>277→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>9792000</v>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>2.61%→2.78%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>177→189</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I80" s="15" t="n">
+        <v>-25612000</v>
+      </c>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>4.92%→4.44%</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>202→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>36080000</v>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>5.99%→6.62%</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>101→112</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="n"/>
+      <c r="H81" s="17" t="n"/>
+      <c r="I81" s="17" t="n"/>
+      <c r="J81" s="17" t="n"/>
+      <c r="K81" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="30">
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="G67:K67"/>
     <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A45:K45"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G48:K48"/>
     <mergeCell ref="G17:K17"/>
+    <mergeCell ref="A54:E54"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="G37:K37"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="A75:K75"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A47:K47"/>
     <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A76:K76"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A53:K53"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="G63:K63"/>
-    <mergeCell ref="G50:K50"/>
-    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="G76:K76"/>
+    <mergeCell ref="G54:K54"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="G31:K31"/>
     <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20261023.xlsx
+++ b/reports/pdf_change_20261023.xlsx
@@ -1054,23 +1054,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>코세스  (신규)</t>
+          <t>엘리스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>3776847940</v>
+        <v>9266394946</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.73%</t>
+          <t>1.14%→5.66%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>0→150</t>
+          <t>50→200</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1098,23 +1098,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>엘리스</t>
+          <t>코세스  (신규)</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9266394946</v>
+        <v>3776847940</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.14%→5.66%</t>
+          <t>0.00%→1.73%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>50→200</t>
+          <t>0→150</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1836,7 +1836,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 50억(4.7%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 0종목  /  매도 2종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 0종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2263,23 +2263,23 @@
       <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-217433922</v>
+        <v>-13526995</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.30%</t>
+          <t>3.61%→3.65%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>13→7</t>
+          <t>1,373→1,367</t>
         </is>
       </c>
     </row>
@@ -2291,23 +2291,23 @@
       <c r="E62" s="17" t="n"/>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-13526995</v>
+        <v>-217433922</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>3.61%→3.65%</t>
+          <t>0.58%→0.30%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>1,373→1,367</t>
+          <t>13→7</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억   ·   현금 7억(2.2%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 4종목  /  매도 5종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B66" s="4" t="n"/>
@@ -2663,7 +2663,7 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      당일 2026-10-23  vs  전영업일 2026-10-22      매수 4종목  /  매도 3종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억      당일 2026-10-23  vs  전영업일 2026-10-22      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
